--- a/artfynd/A 2837-2023 artfynd.xlsx
+++ b/artfynd/A 2837-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2837-2023 artfynd.xlsx
+++ b/artfynd/A 2837-2023 artfynd.xlsx
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119682815</v>
+        <v>119633621</v>
       </c>
       <c r="B11" t="n">
-        <v>56215</v>
+        <v>56208</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1760,20 +1760,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100087</v>
+        <v>100085</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Bechsteins fladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Myotis bechsteinii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1832,22 +1832,22 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ett fåtal inspelningar av denna art gjordes under tre nätters boxavlyssning.</t>
+          <t>En ljudfil med långa S-formade svep (&lt;13 ms) omväxlande med kortare och mer högfrekventa pulser. Artbestämningen har validerats som sannolik bechsteinii av Karin Lundberg Gerell och Hans Baagöe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1995,37 +1995,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119633621</v>
+        <v>119682903</v>
       </c>
       <c r="B13" t="n">
-        <v>56208</v>
+        <v>56218</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100085</v>
+        <v>100092</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bechsteins fladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Myotis bechsteinii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2079,22 +2079,17 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>23:17</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23:17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>En ljudfil med långa S-formade svep (&lt;13 ms) omväxlande med kortare och mer högfrekventa pulser. Artbestämningen har validerats som sannolik bechsteinii av Karin Lundberg Gerell och Hans Baagöe.</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2121,37 +2116,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119682903</v>
+        <v>119682815</v>
       </c>
       <c r="B14" t="n">
-        <v>56218</v>
+        <v>56215</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100092</v>
+        <v>100087</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2218,6 +2213,11 @@
           <t>07:00</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ett fåtal inspelningar av denna art gjordes under tre nätters boxavlyssning.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2837-2023 artfynd.xlsx
+++ b/artfynd/A 2837-2023 artfynd.xlsx
@@ -1748,37 +1748,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119633621</v>
+        <v>119682903</v>
       </c>
       <c r="B11" t="n">
-        <v>56208</v>
+        <v>56218</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100085</v>
+        <v>100092</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bechsteins fladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Myotis bechsteinii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1832,22 +1832,17 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23:17</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>23:17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En ljudfil med långa S-formade svep (&lt;13 ms) omväxlande med kortare och mer högfrekventa pulser. Artbestämningen har validerats som sannolik bechsteinii av Karin Lundberg Gerell och Hans Baagöe.</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1995,37 +1990,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119682903</v>
+        <v>119682815</v>
       </c>
       <c r="B13" t="n">
-        <v>56218</v>
+        <v>56215</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100092</v>
+        <v>100087</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2092,6 +2087,11 @@
           <t>07:00</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ett fåtal inspelningar av denna art gjordes under tre nätters boxavlyssning.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2116,32 +2116,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119682815</v>
+        <v>119683083</v>
       </c>
       <c r="B14" t="n">
-        <v>56215</v>
+        <v>56211</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100087</v>
+        <v>205992</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2213,11 +2213,6 @@
           <t>07:00</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ett fåtal inspelningar av denna art gjordes under tre nätters boxavlyssning.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2242,32 +2237,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119683083</v>
+        <v>119633621</v>
       </c>
       <c r="B15" t="n">
-        <v>56211</v>
+        <v>56208</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205992</v>
+        <v>100085</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Bechsteins fladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Myotis bechsteinii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2326,17 +2321,22 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>En ljudfil med långa S-formade svep (&lt;13 ms) omväxlande med kortare och mer högfrekventa pulser. Artbestämningen har validerats som sannolik bechsteinii av Karin Lundberg Gerell och Hans Baagöe.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 2837-2023 artfynd.xlsx
+++ b/artfynd/A 2837-2023 artfynd.xlsx
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119682903</v>
+        <v>119682818</v>
       </c>
       <c r="B11" t="n">
-        <v>56218</v>
+        <v>56223</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1869,37 +1869,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119682818</v>
+        <v>119682815</v>
       </c>
       <c r="B12" t="n">
-        <v>56223</v>
+        <v>56215</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205995</v>
+        <v>100087</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Fransfladdermus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis nattereri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1966,6 +1966,11 @@
           <t>07:00</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ett fåtal inspelningar av denna art gjordes under tre nätters boxavlyssning.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1990,37 +1995,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119682815</v>
+        <v>119682903</v>
       </c>
       <c r="B13" t="n">
-        <v>56215</v>
+        <v>56218</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100087</v>
+        <v>100092</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2087,11 +2092,6 @@
           <t>07:00</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ett fåtal inspelningar av denna art gjordes under tre nätters boxavlyssning.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2116,32 +2116,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119683083</v>
+        <v>119633621</v>
       </c>
       <c r="B14" t="n">
-        <v>56211</v>
+        <v>56208</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205992</v>
+        <v>100085</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Bechsteins fladdermus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Myotis bechsteinii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2200,17 +2200,22 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>En ljudfil med långa S-formade svep (&lt;13 ms) omväxlande med kortare och mer högfrekventa pulser. Artbestämningen har validerats som sannolik bechsteinii av Karin Lundberg Gerell och Hans Baagöe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2237,32 +2242,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119633621</v>
+        <v>119683083</v>
       </c>
       <c r="B15" t="n">
-        <v>56208</v>
+        <v>56211</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100085</v>
+        <v>205992</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bechsteins fladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Myotis bechsteinii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2321,22 +2326,17 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>23:17</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>23:17</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>En ljudfil med långa S-formade svep (&lt;13 ms) omväxlande med kortare och mer högfrekventa pulser. Artbestämningen har validerats som sannolik bechsteinii av Karin Lundberg Gerell och Hans Baagöe.</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 2837-2023 artfynd.xlsx
+++ b/artfynd/A 2837-2023 artfynd.xlsx
@@ -2366,7 +2366,7 @@
         <v>121274417</v>
       </c>
       <c r="B16" t="n">
-        <v>97027</v>
+        <v>97037</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 2837-2023 artfynd.xlsx
+++ b/artfynd/A 2837-2023 artfynd.xlsx
@@ -2366,7 +2366,7 @@
         <v>121274417</v>
       </c>
       <c r="B16" t="n">
-        <v>97037</v>
+        <v>97050</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 2837-2023 artfynd.xlsx
+++ b/artfynd/A 2837-2023 artfynd.xlsx
@@ -2366,7 +2366,7 @@
         <v>121274417</v>
       </c>
       <c r="B16" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 2837-2023 artfynd.xlsx
+++ b/artfynd/A 2837-2023 artfynd.xlsx
@@ -2366,7 +2366,7 @@
         <v>121274417</v>
       </c>
       <c r="B16" t="n">
-        <v>97051</v>
+        <v>97054</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 2837-2023 artfynd.xlsx
+++ b/artfynd/A 2837-2023 artfynd.xlsx
@@ -2366,7 +2366,7 @@
         <v>121274417</v>
       </c>
       <c r="B16" t="n">
-        <v>97054</v>
+        <v>97060</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 2837-2023 artfynd.xlsx
+++ b/artfynd/A 2837-2023 artfynd.xlsx
@@ -2366,7 +2366,7 @@
         <v>121274417</v>
       </c>
       <c r="B16" t="n">
-        <v>97060</v>
+        <v>97061</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/artfynd/A 2837-2023 artfynd.xlsx
+++ b/artfynd/A 2837-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2473,6 +2473,108 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124112471</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56799</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100038</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skogsduva</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Columba oenas</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Röetved, Sk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>451980</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6224781</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Fjälkestad</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
